--- a/samples/creditcard_out/openapi_field_mapping.xlsx
+++ b/samples/creditcard_out/openapi_field_mapping.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>cfe448a629d4611f</t>
+          <t>020eae2f9e936480</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SOR Polymorphizer 6.6</t>
+          <t>SOR Polymorphizer 6.7</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-09T23:59:47+00:00</t>
+          <t>2026-09-10T00:27:57+00:00</t>
         </is>
       </c>
     </row>

--- a/samples/creditcard_out/openapi_field_mapping.xlsx
+++ b/samples/creditcard_out/openapi_field_mapping.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>020eae2f9e936480</t>
+          <t>12c13392f3009ab1</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SOR Polymorphizer 6.7</t>
+          <t>SOR Polymorphizer 6.8</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10T00:27:57+00:00</t>
+          <t>2026-09-11T05:20:32+00:00</t>
         </is>
       </c>
     </row>
